--- a/doc/excel/apipf.xlsx
+++ b/doc/excel/apipf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suepie/Develop/10_project/aws-atuh-poc/doc/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B22E7AD3-C776-0A41-857B-E39C3E6A1E8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A70F40-BAD7-AB4E-B05F-E7B7CDB8FDFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" activeTab="2" xr2:uid="{3DFCE3C5-E09C-1942-8E2D-30A61B5A45AE}"/>
   </bookViews>

--- a/doc/excel/apipf.xlsx
+++ b/doc/excel/apipf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suepie/Develop/10_project/aws-atuh-poc/doc/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E12B2C35-0589-DC4B-A4F8-2B05BD479900}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7952A9-FF3C-7D42-B681-58C4C6432E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="34200" yWindow="0" windowWidth="38400" windowHeight="21600" firstSheet="5" activeTab="13" xr2:uid="{3DFCE3C5-E09C-1942-8E2D-30A61B5A45AE}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" firstSheet="5" activeTab="13" xr2:uid="{3DFCE3C5-E09C-1942-8E2D-30A61B5A45AE}"/>
   </bookViews>
   <sheets>
     <sheet name="01_表紙・改訂履歴" sheetId="1" r:id="rId1"/>

--- a/doc/excel/apipf.xlsx
+++ b/doc/excel/apipf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suepie/Develop/10_project/aws-atuh-poc/doc/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB7952A9-FF3C-7D42-B681-58C4C6432E0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF9A48A-C753-B740-90B5-61BBA5D21DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" firstSheet="5" activeTab="13" xr2:uid="{3DFCE3C5-E09C-1942-8E2D-30A61B5A45AE}"/>
   </bookViews>
@@ -6463,9 +6463,6 @@
     <t>SQS DLQ 設計</t>
   </si>
   <si>
-    <t>検査 Lambda 用 / Alert Router 用の 2 本。保持期間・再処理手順の方針</t>
-  </si>
-  <si>
     <t>A5-i</t>
   </si>
   <si>
@@ -6697,9 +6694,6 @@
     <t>アカウント列挙 設計</t>
   </si>
   <si>
-    <t>委任ポリシー経由 ListAccounts の呼出仕様・対象 OU フィルタ・ページング</t>
-  </si>
-  <si>
     <t>C1-i</t>
   </si>
   <si>
@@ -6727,9 +6721,6 @@
     <t>AssumeRole/CodeCommit クライアント 設計</t>
   </si>
   <si>
-    <t>ExternalId・一時クレデンシャルのライフサイクル・SDK リトライ（指数バックオフ）設定</t>
-  </si>
-  <si>
     <t>C2-i</t>
   </si>
   <si>
@@ -6754,9 +6745,6 @@
     <t>リポジトリ列挙・差分判定 設計</t>
   </si>
   <si>
-    <t>ListRepositories → GetBranch → lastCheckedCommitId 比較のロジックと「変更あり」判定基準</t>
-  </si>
-  <si>
     <t>C3-i</t>
   </si>
   <si>
@@ -6781,9 +6769,6 @@
     <t>モノレポ対応 設計</t>
   </si>
   <si>
-    <t>GetDifferences の変更パス × pathPrefix 突合仕様（複数アプリ該当時の扱い含む）</t>
-  </si>
-  <si>
     <t>C4-i</t>
   </si>
   <si>
@@ -6805,9 +6790,6 @@
     <t>monitoring.yaml 取得・検証 設計</t>
   </si>
   <si>
-    <t>GetFile（6MB 上限の扱い）・スキーマ検証（W5-2 の JSON Schema 共用）・不備時の分類（メタ不足の種別）</t>
-  </si>
-  <si>
     <t>C5-i</t>
   </si>
   <si>
@@ -6829,9 +6811,6 @@
     <t>台帳同期 設計</t>
   </si>
   <si>
-    <t>registry/{appId}/{env}.json の生成・更新仕様、ETag 条件付き PUT、lastCheckedCommitId は M1 起動成功後にのみ更新（at-least-once）</t>
-  </si>
-  <si>
     <t>C6-i</t>
   </si>
   <si>
@@ -6856,9 +6835,6 @@
     <t>spec 配置 設計</t>
   </si>
   <si>
-    <t>openapi.yaml GetFile → openapi/ Put のキー導出・上書き仕様</t>
-  </si>
-  <si>
     <t>C7-i</t>
   </si>
   <si>
@@ -6880,9 +6856,6 @@
     <t>M1 起動 設計</t>
   </si>
   <si>
-    <t>非同期 Event invoke（payload 仕様・fan-out・DLQ は A5）</t>
-  </si>
-  <si>
     <t>C8-i</t>
   </si>
   <si>
@@ -6904,9 +6877,6 @@
     <t>消滅検知 設計</t>
   </si>
   <si>
-    <t>repo / monitoring.yaml 消滅 → enabled=false + 棚卸しアラート（SNS P2）の判定・通知文面</t>
-  </si>
-  <si>
     <t>C9-i</t>
   </si>
   <si>
@@ -6928,9 +6898,6 @@
     <t>メタ不足アラート 設計</t>
   </si>
   <si>
-    <t>不備種別ごとの通知文面・SNS P2 Publish・再通知抑制（毎巡回で重複させない）</t>
-  </si>
-  <si>
     <t>C10-i</t>
   </si>
   <si>
@@ -6952,9 +6919,6 @@
     <t>部分失敗分離 設計</t>
   </si>
   <si>
-    <t>アカウント単位 try-catch 継続・AccountErrors 集計・ログ出力</t>
-  </si>
-  <si>
     <t>部分失敗分離 実装</t>
   </si>
   <si>
@@ -7012,9 +6976,6 @@
     <t>mode 分岐・fan-out 設計</t>
   </si>
   <si>
-    <t>delta（1 アプリ）/ full（台帳 List → アプリ単位に自己 invoke）の仕様</t>
-  </si>
-  <si>
     <t>K2-i</t>
   </si>
   <si>
@@ -7186,9 +7147,6 @@
     <t>DiscoveryReadRole 設計</t>
   </si>
   <si>
-    <t>ロール設計書: 権限 5 アクション・信頼ポリシー（信頼先 1 本 + ExternalId）・全アカウント同一名のパラメータシート</t>
-  </si>
-  <si>
     <t>S1-i</t>
   </si>
   <si>
@@ -7528,9 +7486,6 @@
     <t>W1 は初日に発注（W1-1 / W1-2 は同梱。W1-3 / W1-4 / W1-6 は個別に並行）。</t>
   </si>
   <si>
-    <t>a5b47d808865cc136318ef04327330ba10731d44</t>
-  </si>
-  <si>
     <t>2026-08-19T07:17:06Z</t>
   </si>
   <si>
@@ -7550,10 +7505,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>4174524f26d385c20bad1598b444ffb487d0f92a</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>0.6</t>
   </si>
   <si>
@@ -7563,6 +7514,54 @@
   <si>
     <t>「14_WBS」を v3 に全面改訂（明細 125 行: W1 6 / W2-A 25 / W2-B 10 / W2-C 65 / W3 9 / W4〜W7 10。設計・実装・単体テストを ID 規約 -d/-i/-t で分離）。「15_WBS集計」を追加</t>
     <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>検査 Lambda 用 / Alert Router 用の 2 本。保持期間・再処理手順の方針。【補足】DLQ（デッドレターキュー）＝処理に失敗したメッセージの退避先。失敗を握り潰さず、後から中身を見て再処理・原因調査するための受け皿</t>
+  </si>
+  <si>
+    <t>委任ポリシー経由 ListAccounts の呼出仕様・対象 OU フィルタ・ページング。【補足】アカウント列挙＝巡回の対象となる App アカウントの一覧を AWS Organizations から毎回取得する処理。手作業のリスト管理をなくし、アカウント追加に自動追随する</t>
+  </si>
+  <si>
+    <t>ExternalId・一時クレデンシャルのライフサイクル・SDK リトライ（指数バックオフ）設定。【補足】AssumeRole＝他アカウントに置かれた読み取り専用ロールの権限を、期限付きで一時的に借りる AWS の標準的な仕組み。これで恒久的な鍵を配らずに App アカウントのリポジトリを読める</t>
+  </si>
+  <si>
+    <t>ListRepositories → GetBranch → lastCheckedCommitId 比較のロジックと「変更あり」判定基準。【補足】リポジトリ列挙＝App アカウント内の CodeCommit リポジトリを一覧し、monitoring.yaml を持つもの（＝監視対象）を見つけること。差分判定＝前回巡回で確認したコミット ID と現在の先端コミット ID を比べ「前回から変更があったか」を判定すること</t>
+  </si>
+  <si>
+    <t>GetDifferences の変更パス × pathPrefix 突合仕様（複数アプリ該当時の扱い含む）。【補足】モノレポ＝1 つのリポジトリに複数アプリのコードを同居させる構成。リポジトリ単位の差分だけでは「どのアプリが変わったか」が分からないため、変更されたファイルのパス（例 apps/expense-api/…）を各アプリの pathPrefix と突き合わせて該当アプリを特定する</t>
+  </si>
+  <si>
+    <t>GetFile（6MB 上限の扱い）・スキーマ検証（W5-2 の JSON Schema 共用）・不備時の分類（メタ不足の種別）。【補足】monitoring.yaml＝アプリが「このリポジトリを監視して」と宣言する設定ファイル（検査先 URL・認証方式などを記載。リポジトリ直下に置く）</t>
+  </si>
+  <si>
+    <t>registry/{appId}/{env}.json の生成・更新仕様、ETag 条件付き PUT、lastCheckedCommitId は M1 起動成功後にのみ更新（at-least-once）。【補足】台帳＝「どのアプリをどう監視するか」を 1 か所に集めた S3 上の管理簿。ETag 条件付き PUT＝「読み込んだ時から誰も更新していなければ書き込む」仕組みで、同時更新による上書き事故を防ぐ。at-least-once＝取りこぼしゼロを優先し、同じ変更を 2 回検査することは許容する方式（検査は読み取りのみなので重複しても無害）</t>
+  </si>
+  <si>
+    <t>openapi.yaml GetFile → openapi/ Put のキー導出・上書き仕様。【補足】spec＝API 仕様書（openapi.yaml。どんな endpoint があるかの一覧）。検査 Lambda が「どこを叩くか」を知るための情報源で、リポジトリから取得して中央の S3 にコピーしておく</t>
+  </si>
+  <si>
+    <t>非同期 Event invoke（payload 仕様・fan-out・DLQ は A5）。【補足】M1＝1 時間毎の巡回で「変更のあったアプリだけ」を自動検査する実行モード（M3＝運用者が手動で全アプリ全量を検査するモードと対をなす）。M1 起動＝発見 Lambda が変更を見つけたアプリを対象に、検査 Lambda を呼び出すこと</t>
+  </si>
+  <si>
+    <t>repo / monitoring.yaml 消滅 → enabled=false + 棚卸しアラート（SNS P2）の判定・通知文面。【補足】消滅検知＝前回まで存在したリポジトリや monitoring.yaml が無くなった（＝アプリ廃止の可能性）ことを検出し、監視を自動停止したうえで「本当に廃止か」の確認を人に促す仕組み</t>
+  </si>
+  <si>
+    <t>不備種別ごとの通知文面・SNS P2 Publish・再通知抑制（毎巡回で重複させない）。【補足】メタ不足＝監視に必要な設定情報（monitoring.yaml そのもの、あるいは検査先 URL・認証方式などの項目）が欠けていて、正しく検査できない状態。放置すると「監視されないアプリ」が生まれるため、アラートで気づかせて設定を直させる</t>
+  </si>
+  <si>
+    <t>アカウント単位 try-catch 継続・AccountErrors 集計・ログ出力。【補足】部分失敗分離＝一部のアカウントで読み取りに失敗しても巡回全体を止めず、残りのアカウントは処理を続けること（失敗はメトリクスで通知し、次の巡回で自然に再試行される）</t>
+  </si>
+  <si>
+    <t>delta（1 アプリ）/ full（台帳 List → アプリ単位に自己 invoke）の仕様。【補足】fan-out＝1 つの処理が対象ごとに自分自身を並列で呼び出して分担する方式。全アプリを 1 回の実行で回すと Lambda の制限時間（15 分）を超え得るため、アプリ単位に分けて起動する</t>
+  </si>
+  <si>
+    <t>ロール設計書: 権限 5 アクション・信頼ポリシー（信頼先 1 本 + ExternalId）・全アカウント同一名のパラメータシート。【補足】DiscoveryReadRole＝各 App アカウントに置く「中央からの読み取り窓口」となる IAM ロール（リポジトリの読み取りのみ可）。StackSets＝CloudFormation を複数アカウントへ一括配布する仕組みで、新規アカウントにも自動で配られる</t>
+  </si>
+  <si>
+    <t>887a5b293f275d1030c6679a6c10a609c36b3d0a</t>
+  </si>
+  <si>
+    <t>9977332ab1ec0512ffa6eb7f9c0cd519760f9477</t>
   </si>
 </sst>
 </file>
@@ -8684,7 +8683,7 @@
         <v>92</v>
       </c>
       <c r="B10" s="41" t="s">
-        <v>2105</v>
+        <v>2089</v>
       </c>
       <c r="C10" s="8" t="s">
         <v>85</v>
@@ -8854,13 +8853,13 @@
     </row>
     <row r="41" spans="1:4" ht="126">
       <c r="A41" s="41" t="s">
-        <v>2106</v>
+        <v>2090</v>
       </c>
       <c r="B41" s="41" t="s">
         <v>1655</v>
       </c>
       <c r="C41" s="41" t="s">
-        <v>2107</v>
+        <v>2091</v>
       </c>
       <c r="D41" s="41" t="s">
         <v>1524</v>
@@ -10318,7 +10317,7 @@
         <v>1616</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>2098</v>
+        <v>2106</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="21">
@@ -10326,7 +10325,7 @@
         <v>1617</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>2099</v>
+        <v>2084</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="63">
@@ -10547,19 +10546,19 @@
     </row>
     <row r="25" spans="1:5" ht="63">
       <c r="A25" s="80" t="s">
-        <v>2100</v>
+        <v>2085</v>
       </c>
       <c r="B25" s="80" t="s">
-        <v>2101</v>
+        <v>2086</v>
       </c>
       <c r="C25" s="80" t="s">
-        <v>2102</v>
+        <v>2087</v>
       </c>
       <c r="D25" s="80" t="s">
-        <v>2103</v>
+        <v>2088</v>
       </c>
       <c r="E25" s="80" t="s">
-        <v>2104</v>
+        <v>2107</v>
       </c>
     </row>
     <row r="27" spans="1:5" ht="210">
@@ -10731,7 +10730,8 @@
     <col min="3" max="3" width="32.85546875" customWidth="1"/>
     <col min="4" max="4" width="74.28515625" customWidth="1"/>
     <col min="5" max="5" width="13.5703125" customWidth="1"/>
-    <col min="6" max="8" width="7.140625" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="7.140625" customWidth="1"/>
     <col min="9" max="9" width="9.7109375" customWidth="1"/>
     <col min="10" max="11" width="11.140625" customWidth="1"/>
     <col min="12" max="12" width="8.85546875" customWidth="1"/>
@@ -11231,7 +11231,7 @@
       <c r="L16" s="63"/>
       <c r="M16" s="63"/>
     </row>
-    <row r="17" spans="1:13" ht="42">
+    <row r="17" spans="1:13" ht="63">
       <c r="A17" s="67" t="s">
         <v>1741</v>
       </c>
@@ -11242,7 +11242,7 @@
         <v>1742</v>
       </c>
       <c r="D17" s="8" t="s">
-        <v>1743</v>
+        <v>2092</v>
       </c>
       <c r="E17" s="8" t="s">
         <v>2</v>
@@ -11263,16 +11263,16 @@
     </row>
     <row r="18" spans="1:13" ht="21">
       <c r="A18" s="67" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="B18" s="8" t="s">
         <v>1664</v>
       </c>
       <c r="C18" s="8" t="s">
+        <v>1744</v>
+      </c>
+      <c r="D18" s="8" t="s">
         <v>1745</v>
-      </c>
-      <c r="D18" s="8" t="s">
-        <v>1746</v>
       </c>
       <c r="E18" s="8" t="s">
         <v>1741</v>
@@ -11293,16 +11293,16 @@
     </row>
     <row r="19" spans="1:13" ht="42">
       <c r="A19" s="67" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="B19" s="8" t="s">
         <v>1664</v>
       </c>
       <c r="C19" s="8" t="s">
+        <v>1747</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>1748</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>1749</v>
       </c>
       <c r="E19" s="8" t="s">
         <v>2</v>
@@ -11323,19 +11323,19 @@
     </row>
     <row r="20" spans="1:13" ht="42">
       <c r="A20" s="67" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="B20" s="8" t="s">
         <v>1664</v>
       </c>
       <c r="C20" s="8" t="s">
+        <v>1750</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>1751</v>
       </c>
-      <c r="D20" s="8" t="s">
-        <v>1752</v>
-      </c>
       <c r="E20" s="8" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="F20" s="67"/>
       <c r="G20" s="65">
@@ -11353,16 +11353,16 @@
     </row>
     <row r="21" spans="1:13" ht="42">
       <c r="A21" s="67" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="B21" s="8" t="s">
         <v>1664</v>
       </c>
       <c r="C21" s="8" t="s">
+        <v>1753</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>1754</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>1755</v>
       </c>
       <c r="E21" s="8" t="s">
         <v>2</v>
@@ -11383,19 +11383,19 @@
     </row>
     <row r="22" spans="1:13" ht="21">
       <c r="A22" s="67" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="B22" s="8" t="s">
         <v>1664</v>
       </c>
       <c r="C22" s="8" t="s">
+        <v>1756</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>1757</v>
       </c>
-      <c r="D22" s="8" t="s">
-        <v>1758</v>
-      </c>
       <c r="E22" s="8" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="F22" s="67"/>
       <c r="G22" s="65">
@@ -11413,16 +11413,16 @@
     </row>
     <row r="23" spans="1:13" ht="42">
       <c r="A23" s="67" t="s">
-        <v>1759</v>
+        <v>1758</v>
       </c>
       <c r="B23" s="8" t="s">
         <v>1664</v>
       </c>
       <c r="C23" s="8" t="s">
+        <v>1759</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>1760</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>1761</v>
       </c>
       <c r="E23" s="8" t="s">
         <v>2</v>
@@ -11443,19 +11443,19 @@
     </row>
     <row r="24" spans="1:13" ht="21">
       <c r="A24" s="67" t="s">
-        <v>1762</v>
+        <v>1761</v>
       </c>
       <c r="B24" s="8" t="s">
         <v>1664</v>
       </c>
       <c r="C24" s="8" t="s">
-        <v>1763</v>
+        <v>1762</v>
       </c>
       <c r="D24" s="8" t="s">
+        <v>1757</v>
+      </c>
+      <c r="E24" s="8" t="s">
         <v>1758</v>
-      </c>
-      <c r="E24" s="8" t="s">
-        <v>1759</v>
       </c>
       <c r="F24" s="67"/>
       <c r="G24" s="65">
@@ -11473,16 +11473,16 @@
     </row>
     <row r="25" spans="1:13" ht="21">
       <c r="A25" s="67" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="B25" s="8" t="s">
         <v>1664</v>
       </c>
       <c r="C25" s="8" t="s">
+        <v>1764</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>1765</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>1766</v>
       </c>
       <c r="E25" s="8" t="s">
         <v>2</v>
@@ -11503,19 +11503,19 @@
     </row>
     <row r="26" spans="1:13" ht="21">
       <c r="A26" s="67" t="s">
-        <v>1767</v>
+        <v>1766</v>
       </c>
       <c r="B26" s="8" t="s">
         <v>1664</v>
       </c>
       <c r="C26" s="8" t="s">
-        <v>1768</v>
+        <v>1767</v>
       </c>
       <c r="D26" s="8" t="s">
-        <v>1758</v>
+        <v>1757</v>
       </c>
       <c r="E26" s="8" t="s">
-        <v>1764</v>
+        <v>1763</v>
       </c>
       <c r="F26" s="67"/>
       <c r="G26" s="65">
@@ -11533,16 +11533,16 @@
     </row>
     <row r="27" spans="1:13" ht="42">
       <c r="A27" s="67" t="s">
-        <v>1769</v>
+        <v>1768</v>
       </c>
       <c r="B27" s="8" t="s">
         <v>1664</v>
       </c>
       <c r="C27" s="8" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>1770</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>1771</v>
       </c>
       <c r="E27" s="8" t="s">
         <v>1635</v>
@@ -11563,16 +11563,16 @@
     </row>
     <row r="28" spans="1:13" ht="42">
       <c r="A28" s="67" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="B28" s="8" t="s">
         <v>1664</v>
       </c>
       <c r="C28" s="8" t="s">
+        <v>1772</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>1773</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>1774</v>
       </c>
       <c r="E28" s="8" t="s">
         <v>1633</v>
@@ -11593,19 +11593,19 @@
     </row>
     <row r="29" spans="1:13" ht="21">
       <c r="A29" s="67" t="s">
-        <v>1775</v>
+        <v>1774</v>
       </c>
       <c r="B29" s="8" t="s">
         <v>1664</v>
       </c>
       <c r="C29" s="8" t="s">
+        <v>1775</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>1776</v>
       </c>
-      <c r="D29" s="8" t="s">
-        <v>1777</v>
-      </c>
       <c r="E29" s="8" t="s">
-        <v>1772</v>
+        <v>1771</v>
       </c>
       <c r="F29" s="67"/>
       <c r="G29" s="65">
@@ -11623,7 +11623,7 @@
     </row>
     <row r="30" spans="1:13" ht="42">
       <c r="A30" s="67" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="B30" s="8" t="s">
         <v>1664</v>
@@ -11632,7 +11632,7 @@
         <v>1665</v>
       </c>
       <c r="D30" s="8" t="s">
-        <v>1779</v>
+        <v>1778</v>
       </c>
       <c r="E30" s="8" t="s">
         <v>2</v>
@@ -11653,16 +11653,16 @@
     </row>
     <row r="31" spans="1:13" ht="42">
       <c r="A31" s="67" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="B31" s="8" t="s">
         <v>1664</v>
       </c>
       <c r="C31" s="8" t="s">
+        <v>1780</v>
+      </c>
+      <c r="D31" s="8" t="s">
         <v>1781</v>
-      </c>
-      <c r="D31" s="8" t="s">
-        <v>1782</v>
       </c>
       <c r="E31" s="8" t="s">
         <v>2</v>
@@ -11683,19 +11683,19 @@
     </row>
     <row r="32" spans="1:13" ht="21">
       <c r="A32" s="67" t="s">
-        <v>1783</v>
+        <v>1782</v>
       </c>
       <c r="B32" s="8" t="s">
         <v>1664</v>
       </c>
       <c r="C32" s="8" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>1784</v>
       </c>
-      <c r="D32" s="8" t="s">
-        <v>1785</v>
-      </c>
       <c r="E32" s="8" t="s">
-        <v>1780</v>
+        <v>1779</v>
       </c>
       <c r="F32" s="67"/>
       <c r="G32" s="65">
@@ -11713,16 +11713,16 @@
     </row>
     <row r="33" spans="1:13" ht="42">
       <c r="A33" s="67" t="s">
-        <v>1786</v>
+        <v>1785</v>
       </c>
       <c r="B33" s="8" t="s">
         <v>1664</v>
       </c>
       <c r="C33" s="8" t="s">
+        <v>1786</v>
+      </c>
+      <c r="D33" s="8" t="s">
         <v>1787</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>1788</v>
       </c>
       <c r="E33" s="8" t="s">
         <v>2</v>
@@ -11766,16 +11766,16 @@
     </row>
     <row r="35" spans="1:13" ht="84">
       <c r="A35" s="67" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B35" s="8" t="s">
         <v>1667</v>
       </c>
       <c r="C35" s="8" t="s">
+        <v>1789</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>1790</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>1791</v>
       </c>
       <c r="E35" s="8" t="s">
         <v>2</v>
@@ -11796,19 +11796,19 @@
     </row>
     <row r="36" spans="1:13" ht="63">
       <c r="A36" s="67" t="s">
-        <v>1792</v>
+        <v>1791</v>
       </c>
       <c r="B36" s="8" t="s">
         <v>1667</v>
       </c>
       <c r="C36" s="8" t="s">
+        <v>1792</v>
+      </c>
+      <c r="D36" s="8" t="s">
         <v>1793</v>
       </c>
-      <c r="D36" s="8" t="s">
+      <c r="E36" s="8" t="s">
         <v>1794</v>
-      </c>
-      <c r="E36" s="8" t="s">
-        <v>1795</v>
       </c>
       <c r="F36" s="67"/>
       <c r="G36" s="65">
@@ -11826,7 +11826,7 @@
     </row>
     <row r="37" spans="1:13" ht="21">
       <c r="A37" s="67" t="s">
-        <v>1796</v>
+        <v>1795</v>
       </c>
       <c r="B37" s="8" t="s">
         <v>1667</v>
@@ -11835,10 +11835,10 @@
         <v>1668</v>
       </c>
       <c r="D37" s="8" t="s">
-        <v>1797</v>
+        <v>1796</v>
       </c>
       <c r="E37" s="8" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="F37" s="67"/>
       <c r="G37" s="65">
@@ -11856,7 +11856,7 @@
     </row>
     <row r="38" spans="1:13" ht="42">
       <c r="A38" s="67" t="s">
-        <v>1798</v>
+        <v>1797</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>1667</v>
@@ -11865,10 +11865,10 @@
         <v>1669</v>
       </c>
       <c r="D38" s="8" t="s">
-        <v>1799</v>
+        <v>1798</v>
       </c>
       <c r="E38" s="8" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="F38" s="67"/>
       <c r="G38" s="65">
@@ -11886,19 +11886,19 @@
     </row>
     <row r="39" spans="1:13" ht="42">
       <c r="A39" s="67" t="s">
-        <v>1800</v>
+        <v>1799</v>
       </c>
       <c r="B39" s="8" t="s">
         <v>1667</v>
       </c>
       <c r="C39" s="8" t="s">
+        <v>1800</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>1801</v>
       </c>
-      <c r="D39" s="8" t="s">
-        <v>1802</v>
-      </c>
       <c r="E39" s="8" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="F39" s="67"/>
       <c r="G39" s="65">
@@ -11916,19 +11916,19 @@
     </row>
     <row r="40" spans="1:13" ht="21">
       <c r="A40" s="67" t="s">
-        <v>1803</v>
+        <v>1802</v>
       </c>
       <c r="B40" s="8" t="s">
         <v>1667</v>
       </c>
       <c r="C40" s="8" t="s">
+        <v>1803</v>
+      </c>
+      <c r="D40" s="8" t="s">
         <v>1804</v>
       </c>
-      <c r="D40" s="8" t="s">
-        <v>1805</v>
-      </c>
       <c r="E40" s="8" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="F40" s="67"/>
       <c r="G40" s="65">
@@ -11946,19 +11946,19 @@
     </row>
     <row r="41" spans="1:13" ht="21">
       <c r="A41" s="67" t="s">
-        <v>1806</v>
+        <v>1805</v>
       </c>
       <c r="B41" s="8" t="s">
         <v>1667</v>
       </c>
       <c r="C41" s="8" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D41" s="8" t="s">
         <v>1807</v>
       </c>
-      <c r="D41" s="8" t="s">
-        <v>1808</v>
-      </c>
       <c r="E41" s="8" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="F41" s="67"/>
       <c r="G41" s="65">
@@ -11976,19 +11976,19 @@
     </row>
     <row r="42" spans="1:13" ht="21">
       <c r="A42" s="67" t="s">
-        <v>1809</v>
+        <v>1808</v>
       </c>
       <c r="B42" s="8" t="s">
         <v>1667</v>
       </c>
       <c r="C42" s="8" t="s">
+        <v>1809</v>
+      </c>
+      <c r="D42" s="8" t="s">
         <v>1810</v>
       </c>
-      <c r="D42" s="8" t="s">
-        <v>1811</v>
-      </c>
       <c r="E42" s="8" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="F42" s="67"/>
       <c r="G42" s="65">
@@ -12006,7 +12006,7 @@
     </row>
     <row r="43" spans="1:13" ht="42">
       <c r="A43" s="67" t="s">
-        <v>1812</v>
+        <v>1811</v>
       </c>
       <c r="B43" s="8" t="s">
         <v>1667</v>
@@ -12015,10 +12015,10 @@
         <v>1670</v>
       </c>
       <c r="D43" s="8" t="s">
-        <v>1813</v>
+        <v>1812</v>
       </c>
       <c r="E43" s="8" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="F43" s="67"/>
       <c r="G43" s="65">
@@ -12036,7 +12036,7 @@
     </row>
     <row r="44" spans="1:13" ht="42">
       <c r="A44" s="67" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="B44" s="8" t="s">
         <v>1667</v>
@@ -12045,7 +12045,7 @@
         <v>1671</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>1815</v>
+        <v>1814</v>
       </c>
       <c r="E44" s="8" t="s">
         <v>1698</v>
@@ -12089,16 +12089,16 @@
     </row>
     <row r="46" spans="1:13" ht="84">
       <c r="A46" s="67" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="B46" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C46" s="8" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D46" s="8" t="s">
         <v>1817</v>
-      </c>
-      <c r="D46" s="8" t="s">
-        <v>1818</v>
       </c>
       <c r="E46" s="8" t="s">
         <v>2</v>
@@ -12117,21 +12117,21 @@
       <c r="L46" s="63"/>
       <c r="M46" s="63"/>
     </row>
-    <row r="47" spans="1:13" ht="42">
+    <row r="47" spans="1:13" ht="63">
       <c r="A47" s="67" t="s">
-        <v>1819</v>
+        <v>1818</v>
       </c>
       <c r="B47" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C47" s="8" t="s">
-        <v>1820</v>
+        <v>1819</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>1821</v>
+        <v>2093</v>
       </c>
       <c r="E47" s="8" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="F47" s="67"/>
       <c r="G47" s="65">
@@ -12149,19 +12149,19 @@
     </row>
     <row r="48" spans="1:13" ht="21">
       <c r="A48" s="67" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="B48" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C48" s="8" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D48" s="8" t="s">
+        <v>1822</v>
+      </c>
+      <c r="E48" s="8" t="s">
         <v>1823</v>
-      </c>
-      <c r="D48" s="8" t="s">
-        <v>1824</v>
-      </c>
-      <c r="E48" s="8" t="s">
-        <v>1825</v>
       </c>
       <c r="F48" s="67"/>
       <c r="G48" s="65">
@@ -12179,19 +12179,19 @@
     </row>
     <row r="49" spans="1:13" ht="21">
       <c r="A49" s="67" t="s">
-        <v>1826</v>
+        <v>1824</v>
       </c>
       <c r="B49" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C49" s="8" t="s">
-        <v>1827</v>
+        <v>1825</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>1828</v>
+        <v>1826</v>
       </c>
       <c r="E49" s="8" t="s">
-        <v>1822</v>
+        <v>1820</v>
       </c>
       <c r="F49" s="67"/>
       <c r="G49" s="65">
@@ -12207,21 +12207,21 @@
       <c r="L49" s="63"/>
       <c r="M49" s="63"/>
     </row>
-    <row r="50" spans="1:13" ht="42">
+    <row r="50" spans="1:13" ht="84">
       <c r="A50" s="67" t="s">
-        <v>1829</v>
+        <v>1827</v>
       </c>
       <c r="B50" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C50" s="8" t="s">
-        <v>1830</v>
+        <v>1828</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>1831</v>
+        <v>2094</v>
       </c>
       <c r="E50" s="8" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="F50" s="67"/>
       <c r="G50" s="65">
@@ -12239,19 +12239,19 @@
     </row>
     <row r="51" spans="1:13" ht="21">
       <c r="A51" s="67" t="s">
-        <v>1832</v>
+        <v>1829</v>
       </c>
       <c r="B51" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C51" s="8" t="s">
-        <v>1833</v>
+        <v>1830</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="E51" s="8" t="s">
-        <v>1834</v>
+        <v>1831</v>
       </c>
       <c r="F51" s="67"/>
       <c r="G51" s="65">
@@ -12269,19 +12269,19 @@
     </row>
     <row r="52" spans="1:13" ht="21">
       <c r="A52" s="67" t="s">
-        <v>1835</v>
+        <v>1832</v>
       </c>
       <c r="B52" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C52" s="8" t="s">
-        <v>1836</v>
+        <v>1833</v>
       </c>
       <c r="D52" s="8" t="s">
-        <v>1837</v>
+        <v>1834</v>
       </c>
       <c r="E52" s="8" t="s">
-        <v>1832</v>
+        <v>1829</v>
       </c>
       <c r="F52" s="67"/>
       <c r="G52" s="65">
@@ -12297,21 +12297,21 @@
       <c r="L52" s="63"/>
       <c r="M52" s="63"/>
     </row>
-    <row r="53" spans="1:13" ht="42">
+    <row r="53" spans="1:13" ht="84">
       <c r="A53" s="67" t="s">
-        <v>1838</v>
+        <v>1835</v>
       </c>
       <c r="B53" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C53" s="8" t="s">
-        <v>1839</v>
+        <v>1836</v>
       </c>
       <c r="D53" s="8" t="s">
-        <v>1840</v>
+        <v>2095</v>
       </c>
       <c r="E53" s="8" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="F53" s="67"/>
       <c r="G53" s="65">
@@ -12329,19 +12329,19 @@
     </row>
     <row r="54" spans="1:13" ht="21">
       <c r="A54" s="67" t="s">
-        <v>1841</v>
+        <v>1837</v>
       </c>
       <c r="B54" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C54" s="8" t="s">
-        <v>1842</v>
+        <v>1838</v>
       </c>
       <c r="D54" s="8" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="E54" s="8" t="s">
-        <v>1843</v>
+        <v>1839</v>
       </c>
       <c r="F54" s="67"/>
       <c r="G54" s="65">
@@ -12359,19 +12359,19 @@
     </row>
     <row r="55" spans="1:13" ht="42">
       <c r="A55" s="67" t="s">
-        <v>1844</v>
+        <v>1840</v>
       </c>
       <c r="B55" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C55" s="8" t="s">
-        <v>1845</v>
+        <v>1841</v>
       </c>
       <c r="D55" s="8" t="s">
-        <v>1846</v>
+        <v>1842</v>
       </c>
       <c r="E55" s="8" t="s">
-        <v>1841</v>
+        <v>1837</v>
       </c>
       <c r="F55" s="67"/>
       <c r="G55" s="65">
@@ -12387,21 +12387,21 @@
       <c r="L55" s="63"/>
       <c r="M55" s="63"/>
     </row>
-    <row r="56" spans="1:13" ht="42">
+    <row r="56" spans="1:13" ht="84">
       <c r="A56" s="67" t="s">
-        <v>1847</v>
+        <v>1843</v>
       </c>
       <c r="B56" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C56" s="8" t="s">
-        <v>1848</v>
+        <v>1844</v>
       </c>
       <c r="D56" s="8" t="s">
-        <v>1849</v>
+        <v>2096</v>
       </c>
       <c r="E56" s="8" t="s">
-        <v>1838</v>
+        <v>1835</v>
       </c>
       <c r="F56" s="67"/>
       <c r="G56" s="65">
@@ -12419,19 +12419,19 @@
     </row>
     <row r="57" spans="1:13" ht="21">
       <c r="A57" s="67" t="s">
-        <v>1850</v>
+        <v>1845</v>
       </c>
       <c r="B57" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C57" s="8" t="s">
-        <v>1851</v>
+        <v>1846</v>
       </c>
       <c r="D57" s="8" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="E57" s="8" t="s">
-        <v>1847</v>
+        <v>1843</v>
       </c>
       <c r="F57" s="67"/>
       <c r="G57" s="65">
@@ -12449,19 +12449,19 @@
     </row>
     <row r="58" spans="1:13" ht="42">
       <c r="A58" s="67" t="s">
-        <v>1852</v>
+        <v>1847</v>
       </c>
       <c r="B58" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C58" s="8" t="s">
-        <v>1853</v>
+        <v>1848</v>
       </c>
       <c r="D58" s="8" t="s">
-        <v>1854</v>
+        <v>1849</v>
       </c>
       <c r="E58" s="8" t="s">
-        <v>1850</v>
+        <v>1845</v>
       </c>
       <c r="F58" s="67"/>
       <c r="G58" s="65">
@@ -12477,21 +12477,21 @@
       <c r="L58" s="63"/>
       <c r="M58" s="63"/>
     </row>
-    <row r="59" spans="1:13" ht="42">
+    <row r="59" spans="1:13" ht="63">
       <c r="A59" s="67" t="s">
-        <v>1855</v>
+        <v>1850</v>
       </c>
       <c r="B59" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C59" s="8" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="D59" s="8" t="s">
-        <v>1857</v>
+        <v>2097</v>
       </c>
       <c r="E59" s="8" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="F59" s="67"/>
       <c r="G59" s="65">
@@ -12509,19 +12509,19 @@
     </row>
     <row r="60" spans="1:13" ht="21">
       <c r="A60" s="67" t="s">
-        <v>1858</v>
+        <v>1852</v>
       </c>
       <c r="B60" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C60" s="8" t="s">
-        <v>1859</v>
+        <v>1853</v>
       </c>
       <c r="D60" s="8" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="E60" s="8" t="s">
-        <v>1855</v>
+        <v>1850</v>
       </c>
       <c r="F60" s="67"/>
       <c r="G60" s="65">
@@ -12539,19 +12539,19 @@
     </row>
     <row r="61" spans="1:13" ht="42">
       <c r="A61" s="67" t="s">
-        <v>1860</v>
+        <v>1854</v>
       </c>
       <c r="B61" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C61" s="8" t="s">
-        <v>1861</v>
+        <v>1855</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>1862</v>
+        <v>1856</v>
       </c>
       <c r="E61" s="8" t="s">
-        <v>1858</v>
+        <v>1852</v>
       </c>
       <c r="F61" s="67"/>
       <c r="G61" s="65">
@@ -12567,21 +12567,21 @@
       <c r="L61" s="63"/>
       <c r="M61" s="63"/>
     </row>
-    <row r="62" spans="1:13" ht="63">
+    <row r="62" spans="1:13" ht="126">
       <c r="A62" s="67" t="s">
-        <v>1863</v>
+        <v>1857</v>
       </c>
       <c r="B62" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C62" s="8" t="s">
-        <v>1864</v>
+        <v>1858</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>1865</v>
+        <v>2098</v>
       </c>
       <c r="E62" s="8" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="F62" s="67"/>
       <c r="G62" s="65">
@@ -12599,19 +12599,19 @@
     </row>
     <row r="63" spans="1:13" ht="21">
       <c r="A63" s="67" t="s">
-        <v>1866</v>
+        <v>1859</v>
       </c>
       <c r="B63" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C63" s="8" t="s">
-        <v>1867</v>
+        <v>1860</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="E63" s="8" t="s">
-        <v>1868</v>
+        <v>1861</v>
       </c>
       <c r="F63" s="67"/>
       <c r="G63" s="65">
@@ -12629,19 +12629,19 @@
     </row>
     <row r="64" spans="1:13" ht="42">
       <c r="A64" s="67" t="s">
-        <v>1869</v>
+        <v>1862</v>
       </c>
       <c r="B64" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C64" s="8" t="s">
-        <v>1870</v>
+        <v>1863</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>1871</v>
+        <v>1864</v>
       </c>
       <c r="E64" s="8" t="s">
-        <v>1866</v>
+        <v>1859</v>
       </c>
       <c r="F64" s="67"/>
       <c r="G64" s="65">
@@ -12657,21 +12657,21 @@
       <c r="L64" s="63"/>
       <c r="M64" s="63"/>
     </row>
-    <row r="65" spans="1:13" ht="42">
+    <row r="65" spans="1:13" ht="63">
       <c r="A65" s="67" t="s">
-        <v>1872</v>
+        <v>1865</v>
       </c>
       <c r="B65" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C65" s="8" t="s">
-        <v>1873</v>
+        <v>1866</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>1874</v>
+        <v>2099</v>
       </c>
       <c r="E65" s="8" t="s">
-        <v>1855</v>
+        <v>1850</v>
       </c>
       <c r="F65" s="67"/>
       <c r="G65" s="65">
@@ -12689,19 +12689,19 @@
     </row>
     <row r="66" spans="1:13" ht="21">
       <c r="A66" s="67" t="s">
-        <v>1875</v>
+        <v>1867</v>
       </c>
       <c r="B66" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C66" s="8" t="s">
-        <v>1876</v>
+        <v>1868</v>
       </c>
       <c r="D66" s="8" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="E66" s="8" t="s">
-        <v>1872</v>
+        <v>1865</v>
       </c>
       <c r="F66" s="67"/>
       <c r="G66" s="65">
@@ -12719,19 +12719,19 @@
     </row>
     <row r="67" spans="1:13" ht="21">
       <c r="A67" s="67" t="s">
-        <v>1877</v>
+        <v>1869</v>
       </c>
       <c r="B67" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C67" s="8" t="s">
-        <v>1878</v>
+        <v>1870</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>1879</v>
+        <v>1871</v>
       </c>
       <c r="E67" s="8" t="s">
-        <v>1875</v>
+        <v>1867</v>
       </c>
       <c r="F67" s="67"/>
       <c r="G67" s="65">
@@ -12747,21 +12747,21 @@
       <c r="L67" s="63"/>
       <c r="M67" s="63"/>
     </row>
-    <row r="68" spans="1:13" ht="42">
+    <row r="68" spans="1:13" ht="84">
       <c r="A68" s="67" t="s">
-        <v>1880</v>
+        <v>1872</v>
       </c>
       <c r="B68" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C68" s="8" t="s">
-        <v>1881</v>
+        <v>1873</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>1882</v>
+        <v>2100</v>
       </c>
       <c r="E68" s="8" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="F68" s="67"/>
       <c r="G68" s="65">
@@ -12779,19 +12779,19 @@
     </row>
     <row r="69" spans="1:13" ht="21">
       <c r="A69" s="67" t="s">
-        <v>1883</v>
+        <v>1874</v>
       </c>
       <c r="B69" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>1884</v>
+        <v>1875</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="E69" s="8" t="s">
-        <v>1880</v>
+        <v>1872</v>
       </c>
       <c r="F69" s="67"/>
       <c r="G69" s="65">
@@ -12809,19 +12809,19 @@
     </row>
     <row r="70" spans="1:13" ht="21">
       <c r="A70" s="67" t="s">
-        <v>1885</v>
+        <v>1876</v>
       </c>
       <c r="B70" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>1886</v>
+        <v>1877</v>
       </c>
       <c r="D70" s="8" t="s">
-        <v>1887</v>
+        <v>1878</v>
       </c>
       <c r="E70" s="8" t="s">
-        <v>1883</v>
+        <v>1874</v>
       </c>
       <c r="F70" s="67"/>
       <c r="G70" s="65">
@@ -12837,21 +12837,21 @@
       <c r="L70" s="63"/>
       <c r="M70" s="63"/>
     </row>
-    <row r="71" spans="1:13" ht="42">
+    <row r="71" spans="1:13" ht="84">
       <c r="A71" s="67" t="s">
-        <v>1888</v>
+        <v>1879</v>
       </c>
       <c r="B71" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>1889</v>
+        <v>1880</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>1890</v>
+        <v>2101</v>
       </c>
       <c r="E71" s="8" t="s">
-        <v>1838</v>
+        <v>1835</v>
       </c>
       <c r="F71" s="67"/>
       <c r="G71" s="65">
@@ -12869,19 +12869,19 @@
     </row>
     <row r="72" spans="1:13" ht="21">
       <c r="A72" s="67" t="s">
-        <v>1891</v>
+        <v>1881</v>
       </c>
       <c r="B72" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C72" s="8" t="s">
-        <v>1892</v>
+        <v>1882</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="E72" s="8" t="s">
-        <v>1888</v>
+        <v>1879</v>
       </c>
       <c r="F72" s="67"/>
       <c r="G72" s="65">
@@ -12899,19 +12899,19 @@
     </row>
     <row r="73" spans="1:13" ht="21">
       <c r="A73" s="67" t="s">
-        <v>1893</v>
+        <v>1883</v>
       </c>
       <c r="B73" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>1894</v>
+        <v>1884</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>1895</v>
+        <v>1885</v>
       </c>
       <c r="E73" s="8" t="s">
-        <v>1891</v>
+        <v>1881</v>
       </c>
       <c r="F73" s="67"/>
       <c r="G73" s="65">
@@ -12927,21 +12927,21 @@
       <c r="L73" s="63"/>
       <c r="M73" s="63"/>
     </row>
-    <row r="74" spans="1:13" ht="42">
+    <row r="74" spans="1:13" ht="84">
       <c r="A74" s="67" t="s">
-        <v>1896</v>
+        <v>1886</v>
       </c>
       <c r="B74" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C74" s="8" t="s">
-        <v>1897</v>
+        <v>1887</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>1898</v>
+        <v>2102</v>
       </c>
       <c r="E74" s="8" t="s">
-        <v>1855</v>
+        <v>1850</v>
       </c>
       <c r="F74" s="67"/>
       <c r="G74" s="65">
@@ -12959,19 +12959,19 @@
     </row>
     <row r="75" spans="1:13" ht="21">
       <c r="A75" s="67" t="s">
-        <v>1899</v>
+        <v>1888</v>
       </c>
       <c r="B75" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>1900</v>
+        <v>1889</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="E75" s="8" t="s">
-        <v>1896</v>
+        <v>1886</v>
       </c>
       <c r="F75" s="67"/>
       <c r="G75" s="65">
@@ -12989,19 +12989,19 @@
     </row>
     <row r="76" spans="1:13" ht="21">
       <c r="A76" s="67" t="s">
-        <v>1901</v>
+        <v>1890</v>
       </c>
       <c r="B76" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C76" s="8" t="s">
-        <v>1902</v>
+        <v>1891</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>1903</v>
+        <v>1892</v>
       </c>
       <c r="E76" s="8" t="s">
-        <v>1899</v>
+        <v>1888</v>
       </c>
       <c r="F76" s="67"/>
       <c r="G76" s="65">
@@ -13017,21 +13017,21 @@
       <c r="L76" s="63"/>
       <c r="M76" s="63"/>
     </row>
-    <row r="77" spans="1:13" ht="42">
+    <row r="77" spans="1:13" ht="63">
       <c r="A77" s="67" t="s">
-        <v>1904</v>
+        <v>1893</v>
       </c>
       <c r="B77" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C77" s="8" t="s">
-        <v>1905</v>
+        <v>1894</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>1906</v>
+        <v>2103</v>
       </c>
       <c r="E77" s="8" t="s">
-        <v>1816</v>
+        <v>1815</v>
       </c>
       <c r="F77" s="67"/>
       <c r="G77" s="65">
@@ -13049,19 +13049,19 @@
     </row>
     <row r="78" spans="1:13" ht="21">
       <c r="A78" s="67" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="B78" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>1907</v>
+        <v>1895</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>1908</v>
+        <v>1896</v>
       </c>
       <c r="E78" s="8" t="s">
-        <v>1904</v>
+        <v>1893</v>
       </c>
       <c r="F78" s="67"/>
       <c r="G78" s="65">
@@ -13079,19 +13079,19 @@
     </row>
     <row r="79" spans="1:13" ht="21">
       <c r="A79" s="67" t="s">
-        <v>1909</v>
+        <v>1897</v>
       </c>
       <c r="B79" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>1910</v>
+        <v>1898</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>1911</v>
+        <v>1899</v>
       </c>
       <c r="E79" s="8" t="s">
-        <v>1795</v>
+        <v>1794</v>
       </c>
       <c r="F79" s="67"/>
       <c r="G79" s="65">
@@ -13109,7 +13109,7 @@
     </row>
     <row r="80" spans="1:13" ht="84">
       <c r="A80" s="76" t="s">
-        <v>1912</v>
+        <v>1900</v>
       </c>
       <c r="B80" s="72"/>
       <c r="C80" s="72"/>
@@ -13132,16 +13132,16 @@
     </row>
     <row r="81" spans="1:13" ht="63">
       <c r="A81" s="67" t="s">
-        <v>1913</v>
+        <v>1901</v>
       </c>
       <c r="B81" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>1914</v>
+        <v>1902</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>1915</v>
+        <v>1903</v>
       </c>
       <c r="E81" s="8" t="s">
         <v>2</v>
@@ -13162,19 +13162,19 @@
     </row>
     <row r="82" spans="1:13" ht="42">
       <c r="A82" s="67" t="s">
-        <v>1916</v>
+        <v>1904</v>
       </c>
       <c r="B82" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>1917</v>
+        <v>1905</v>
       </c>
       <c r="D82" s="8" t="s">
-        <v>1918</v>
+        <v>1906</v>
       </c>
       <c r="E82" s="8" t="s">
-        <v>1913</v>
+        <v>1901</v>
       </c>
       <c r="F82" s="67"/>
       <c r="G82" s="65">
@@ -13192,19 +13192,19 @@
     </row>
     <row r="83" spans="1:13" ht="21">
       <c r="A83" s="67" t="s">
-        <v>1919</v>
+        <v>1907</v>
       </c>
       <c r="B83" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C83" s="8" t="s">
-        <v>1920</v>
+        <v>1908</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="E83" s="8" t="s">
-        <v>1916</v>
+        <v>1904</v>
       </c>
       <c r="F83" s="67"/>
       <c r="G83" s="65">
@@ -13222,19 +13222,19 @@
     </row>
     <row r="84" spans="1:13" ht="42">
       <c r="A84" s="67" t="s">
-        <v>1921</v>
+        <v>1909</v>
       </c>
       <c r="B84" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C84" s="8" t="s">
-        <v>1922</v>
+        <v>1910</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>1923</v>
+        <v>1911</v>
       </c>
       <c r="E84" s="8" t="s">
-        <v>1919</v>
+        <v>1907</v>
       </c>
       <c r="F84" s="67"/>
       <c r="G84" s="65">
@@ -13250,21 +13250,21 @@
       <c r="L84" s="63"/>
       <c r="M84" s="63"/>
     </row>
-    <row r="85" spans="1:13" ht="42">
+    <row r="85" spans="1:13" ht="63">
       <c r="A85" s="67" t="s">
-        <v>1924</v>
+        <v>1912</v>
       </c>
       <c r="B85" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>1925</v>
+        <v>1913</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>1926</v>
+        <v>2104</v>
       </c>
       <c r="E85" s="8" t="s">
-        <v>1913</v>
+        <v>1901</v>
       </c>
       <c r="F85" s="67"/>
       <c r="G85" s="65">
@@ -13282,19 +13282,19 @@
     </row>
     <row r="86" spans="1:13" ht="21">
       <c r="A86" s="67" t="s">
-        <v>1927</v>
+        <v>1914</v>
       </c>
       <c r="B86" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C86" s="8" t="s">
-        <v>1928</v>
+        <v>1915</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="E86" s="8" t="s">
-        <v>1924</v>
+        <v>1912</v>
       </c>
       <c r="F86" s="67"/>
       <c r="G86" s="65">
@@ -13312,19 +13312,19 @@
     </row>
     <row r="87" spans="1:13" ht="21">
       <c r="A87" s="67" t="s">
-        <v>1929</v>
+        <v>1916</v>
       </c>
       <c r="B87" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C87" s="8" t="s">
-        <v>1930</v>
+        <v>1917</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>1931</v>
+        <v>1918</v>
       </c>
       <c r="E87" s="8" t="s">
-        <v>1927</v>
+        <v>1914</v>
       </c>
       <c r="F87" s="67"/>
       <c r="G87" s="65">
@@ -13342,19 +13342,19 @@
     </row>
     <row r="88" spans="1:13" ht="42">
       <c r="A88" s="67" t="s">
-        <v>1932</v>
+        <v>1919</v>
       </c>
       <c r="B88" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C88" s="8" t="s">
-        <v>1933</v>
+        <v>1920</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>1934</v>
+        <v>1921</v>
       </c>
       <c r="E88" s="8" t="s">
-        <v>1913</v>
+        <v>1901</v>
       </c>
       <c r="F88" s="67"/>
       <c r="G88" s="65">
@@ -13372,19 +13372,19 @@
     </row>
     <row r="89" spans="1:13" ht="21">
       <c r="A89" s="67" t="s">
-        <v>1935</v>
+        <v>1922</v>
       </c>
       <c r="B89" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C89" s="8" t="s">
-        <v>1936</v>
+        <v>1923</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="E89" s="8" t="s">
-        <v>1937</v>
+        <v>1924</v>
       </c>
       <c r="F89" s="67"/>
       <c r="G89" s="65">
@@ -13402,19 +13402,19 @@
     </row>
     <row r="90" spans="1:13" ht="21">
       <c r="A90" s="67" t="s">
-        <v>1938</v>
+        <v>1925</v>
       </c>
       <c r="B90" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C90" s="8" t="s">
-        <v>1939</v>
+        <v>1926</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>1940</v>
+        <v>1927</v>
       </c>
       <c r="E90" s="8" t="s">
-        <v>1935</v>
+        <v>1922</v>
       </c>
       <c r="F90" s="67"/>
       <c r="G90" s="65">
@@ -13432,19 +13432,19 @@
     </row>
     <row r="91" spans="1:13" ht="42">
       <c r="A91" s="67" t="s">
-        <v>1941</v>
+        <v>1928</v>
       </c>
       <c r="B91" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C91" s="8" t="s">
-        <v>1942</v>
+        <v>1929</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>1943</v>
+        <v>1930</v>
       </c>
       <c r="E91" s="8" t="s">
-        <v>1944</v>
+        <v>1931</v>
       </c>
       <c r="F91" s="67"/>
       <c r="G91" s="65">
@@ -13462,19 +13462,19 @@
     </row>
     <row r="92" spans="1:13" ht="21">
       <c r="A92" s="67" t="s">
-        <v>1945</v>
+        <v>1932</v>
       </c>
       <c r="B92" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C92" s="8" t="s">
-        <v>1946</v>
+        <v>1933</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>1947</v>
+        <v>1934</v>
       </c>
       <c r="E92" s="8" t="s">
-        <v>1941</v>
+        <v>1928</v>
       </c>
       <c r="F92" s="67"/>
       <c r="G92" s="65">
@@ -13492,19 +13492,19 @@
     </row>
     <row r="93" spans="1:13" ht="42">
       <c r="A93" s="67" t="s">
-        <v>1948</v>
+        <v>1935</v>
       </c>
       <c r="B93" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>1949</v>
+        <v>1936</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>1950</v>
+        <v>1937</v>
       </c>
       <c r="E93" s="8" t="s">
-        <v>1945</v>
+        <v>1932</v>
       </c>
       <c r="F93" s="67"/>
       <c r="G93" s="65">
@@ -13522,7 +13522,7 @@
     </row>
     <row r="94" spans="1:13" ht="84">
       <c r="A94" s="76" t="s">
-        <v>1951</v>
+        <v>1938</v>
       </c>
       <c r="B94" s="72"/>
       <c r="C94" s="72"/>
@@ -13545,16 +13545,16 @@
     </row>
     <row r="95" spans="1:13" ht="42">
       <c r="A95" s="67" t="s">
-        <v>1952</v>
+        <v>1939</v>
       </c>
       <c r="B95" s="8" t="s">
         <v>1675</v>
       </c>
       <c r="C95" s="8" t="s">
-        <v>1953</v>
+        <v>1940</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>1954</v>
+        <v>1941</v>
       </c>
       <c r="E95" s="8" t="s">
         <v>2</v>
@@ -13575,19 +13575,19 @@
     </row>
     <row r="96" spans="1:13" ht="42">
       <c r="A96" s="67" t="s">
-        <v>1955</v>
+        <v>1942</v>
       </c>
       <c r="B96" s="8" t="s">
         <v>1675</v>
       </c>
       <c r="C96" s="8" t="s">
-        <v>1956</v>
+        <v>1943</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>1957</v>
+        <v>1944</v>
       </c>
       <c r="E96" s="8" t="s">
-        <v>1958</v>
+        <v>1945</v>
       </c>
       <c r="F96" s="67"/>
       <c r="G96" s="65">
@@ -13605,19 +13605,19 @@
     </row>
     <row r="97" spans="1:13" ht="42">
       <c r="A97" s="67" t="s">
-        <v>1959</v>
+        <v>1946</v>
       </c>
       <c r="B97" s="8" t="s">
         <v>1675</v>
       </c>
       <c r="C97" s="8" t="s">
-        <v>1960</v>
+        <v>1947</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>1961</v>
+        <v>1948</v>
       </c>
       <c r="E97" s="8" t="s">
-        <v>1958</v>
+        <v>1945</v>
       </c>
       <c r="F97" s="67"/>
       <c r="G97" s="65">
@@ -13635,7 +13635,7 @@
     </row>
     <row r="98" spans="1:13" ht="21">
       <c r="A98" s="67" t="s">
-        <v>1962</v>
+        <v>1949</v>
       </c>
       <c r="B98" s="8" t="s">
         <v>1675</v>
@@ -13644,7 +13644,7 @@
         <v>1676</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>1963</v>
+        <v>1950</v>
       </c>
       <c r="E98" s="8" t="s">
         <v>1738</v>
@@ -13665,16 +13665,16 @@
     </row>
     <row r="99" spans="1:13" ht="42">
       <c r="A99" s="67" t="s">
-        <v>1964</v>
+        <v>1951</v>
       </c>
       <c r="B99" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C99" s="8" t="s">
-        <v>1965</v>
+        <v>1952</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>1966</v>
+        <v>1953</v>
       </c>
       <c r="E99" s="8" t="s">
         <v>1635</v>
@@ -13695,19 +13695,19 @@
     </row>
     <row r="100" spans="1:13" ht="42">
       <c r="A100" s="67" t="s">
-        <v>1967</v>
+        <v>1954</v>
       </c>
       <c r="B100" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C100" s="8" t="s">
-        <v>1968</v>
+        <v>1955</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>1969</v>
+        <v>1956</v>
       </c>
       <c r="E100" s="8" t="s">
-        <v>1970</v>
+        <v>1957</v>
       </c>
       <c r="F100" s="67"/>
       <c r="G100" s="65">
@@ -13725,19 +13725,19 @@
     </row>
     <row r="101" spans="1:13" ht="42">
       <c r="A101" s="67" t="s">
-        <v>1971</v>
+        <v>1958</v>
       </c>
       <c r="B101" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C101" s="8" t="s">
-        <v>1972</v>
+        <v>1959</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>1973</v>
+        <v>1960</v>
       </c>
       <c r="E101" s="8" t="s">
-        <v>1964</v>
+        <v>1951</v>
       </c>
       <c r="F101" s="67"/>
       <c r="G101" s="65">
@@ -13755,16 +13755,16 @@
     </row>
     <row r="102" spans="1:13" ht="42">
       <c r="A102" s="67" t="s">
-        <v>1974</v>
+        <v>1961</v>
       </c>
       <c r="B102" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C102" s="8" t="s">
-        <v>1975</v>
+        <v>1962</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>1976</v>
+        <v>1963</v>
       </c>
       <c r="E102" s="8" t="s">
         <v>1636</v>
@@ -13785,19 +13785,19 @@
     </row>
     <row r="103" spans="1:13" ht="21">
       <c r="A103" s="67" t="s">
-        <v>1977</v>
+        <v>1964</v>
       </c>
       <c r="B103" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C103" s="8" t="s">
-        <v>1978</v>
+        <v>1965</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>1824</v>
+        <v>1822</v>
       </c>
       <c r="E103" s="8" t="s">
-        <v>1974</v>
+        <v>1961</v>
       </c>
       <c r="F103" s="67"/>
       <c r="G103" s="65">
@@ -13815,19 +13815,19 @@
     </row>
     <row r="104" spans="1:13" ht="21">
       <c r="A104" s="67" t="s">
-        <v>1979</v>
+        <v>1966</v>
       </c>
       <c r="B104" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C104" s="8" t="s">
-        <v>1980</v>
+        <v>1967</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>1981</v>
+        <v>1968</v>
       </c>
       <c r="E104" s="8" t="s">
-        <v>1977</v>
+        <v>1964</v>
       </c>
       <c r="F104" s="67"/>
       <c r="G104" s="65">
@@ -13843,18 +13843,18 @@
       <c r="L104" s="63"/>
       <c r="M104" s="63"/>
     </row>
-    <row r="105" spans="1:13" ht="42">
+    <row r="105" spans="1:13" ht="105">
       <c r="A105" s="67" t="s">
-        <v>1982</v>
+        <v>1969</v>
       </c>
       <c r="B105" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C105" s="8" t="s">
-        <v>1983</v>
+        <v>1970</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>1984</v>
+        <v>2105</v>
       </c>
       <c r="E105" s="8" t="s">
         <v>2</v>
@@ -13875,19 +13875,19 @@
     </row>
     <row r="106" spans="1:13" ht="42">
       <c r="A106" s="67" t="s">
-        <v>1985</v>
+        <v>1971</v>
       </c>
       <c r="B106" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C106" s="8" t="s">
-        <v>1986</v>
+        <v>1972</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>1987</v>
+        <v>1973</v>
       </c>
       <c r="E106" s="8" t="s">
-        <v>1982</v>
+        <v>1969</v>
       </c>
       <c r="F106" s="67"/>
       <c r="G106" s="65">
@@ -13905,19 +13905,19 @@
     </row>
     <row r="107" spans="1:13" ht="42">
       <c r="A107" s="67" t="s">
-        <v>1988</v>
+        <v>1974</v>
       </c>
       <c r="B107" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C107" s="8" t="s">
-        <v>1989</v>
+        <v>1975</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>1990</v>
+        <v>1976</v>
       </c>
       <c r="E107" s="8" t="s">
-        <v>1985</v>
+        <v>1971</v>
       </c>
       <c r="F107" s="67"/>
       <c r="G107" s="65">
@@ -13935,16 +13935,16 @@
     </row>
     <row r="108" spans="1:13" ht="63">
       <c r="A108" s="67" t="s">
-        <v>1991</v>
+        <v>1977</v>
       </c>
       <c r="B108" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C108" s="8" t="s">
-        <v>1992</v>
+        <v>1978</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>1993</v>
+        <v>1979</v>
       </c>
       <c r="E108" s="8" t="s">
         <v>2</v>
@@ -13965,19 +13965,19 @@
     </row>
     <row r="109" spans="1:13" ht="21">
       <c r="A109" s="67" t="s">
-        <v>1994</v>
+        <v>1980</v>
       </c>
       <c r="B109" s="8" t="s">
         <v>36</v>
       </c>
       <c r="C109" s="8" t="s">
-        <v>1995</v>
+        <v>1981</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>1996</v>
+        <v>1982</v>
       </c>
       <c r="E109" s="8" t="s">
-        <v>1991</v>
+        <v>1977</v>
       </c>
       <c r="F109" s="67"/>
       <c r="G109" s="65">
@@ -13995,7 +13995,7 @@
     </row>
     <row r="110" spans="1:13" ht="21">
       <c r="A110" s="67" t="s">
-        <v>1997</v>
+        <v>1983</v>
       </c>
       <c r="B110" s="8" t="s">
         <v>36</v>
@@ -14004,10 +14004,10 @@
         <v>1677</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>1998</v>
+        <v>1984</v>
       </c>
       <c r="E110" s="8" t="s">
-        <v>1994</v>
+        <v>1980</v>
       </c>
       <c r="F110" s="67"/>
       <c r="G110" s="65">
@@ -14025,7 +14025,7 @@
     </row>
     <row r="111" spans="1:13" ht="42">
       <c r="A111" s="67" t="s">
-        <v>1999</v>
+        <v>1985</v>
       </c>
       <c r="B111" s="8" t="s">
         <v>1674</v>
@@ -14034,10 +14034,10 @@
         <v>1678</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>2000</v>
+        <v>1986</v>
       </c>
       <c r="E111" s="8" t="s">
-        <v>1997</v>
+        <v>1983</v>
       </c>
       <c r="F111" s="67"/>
       <c r="G111" s="65">
@@ -14055,19 +14055,19 @@
     </row>
     <row r="112" spans="1:13" ht="42">
       <c r="A112" s="67" t="s">
-        <v>2001</v>
+        <v>1987</v>
       </c>
       <c r="B112" s="8" t="s">
         <v>1673</v>
       </c>
       <c r="C112" s="8" t="s">
-        <v>2002</v>
+        <v>1988</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>2003</v>
+        <v>1989</v>
       </c>
       <c r="E112" s="8" t="s">
-        <v>2004</v>
+        <v>1990</v>
       </c>
       <c r="F112" s="67"/>
       <c r="G112" s="65">
@@ -14085,7 +14085,7 @@
     </row>
     <row r="113" spans="1:13" ht="63">
       <c r="A113" s="76" t="s">
-        <v>2005</v>
+        <v>1991</v>
       </c>
       <c r="B113" s="72"/>
       <c r="C113" s="72"/>
@@ -14114,10 +14114,10 @@
         <v>1674</v>
       </c>
       <c r="C114" s="8" t="s">
-        <v>2006</v>
+        <v>1992</v>
       </c>
       <c r="D114" s="8" t="s">
-        <v>2007</v>
+        <v>1993</v>
       </c>
       <c r="E114" s="8" t="s">
         <v>1638</v>
@@ -14144,13 +14144,13 @@
         <v>1674</v>
       </c>
       <c r="C115" s="8" t="s">
-        <v>2008</v>
+        <v>1994</v>
       </c>
       <c r="D115" s="8" t="s">
-        <v>2009</v>
+        <v>1995</v>
       </c>
       <c r="E115" s="8" t="s">
-        <v>2010</v>
+        <v>1996</v>
       </c>
       <c r="F115" s="67"/>
       <c r="G115" s="65">
@@ -14170,16 +14170,16 @@
     </row>
     <row r="116" spans="1:13" ht="84">
       <c r="A116" s="67" t="s">
-        <v>2011</v>
+        <v>1997</v>
       </c>
       <c r="B116" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C116" s="8" t="s">
-        <v>2012</v>
+        <v>1998</v>
       </c>
       <c r="D116" s="8" t="s">
-        <v>2013</v>
+        <v>1999</v>
       </c>
       <c r="E116" s="8" t="s">
         <v>1639</v>
@@ -14202,16 +14202,16 @@
     </row>
     <row r="117" spans="1:13" ht="126">
       <c r="A117" s="67" t="s">
-        <v>2014</v>
+        <v>2000</v>
       </c>
       <c r="B117" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C117" s="8" t="s">
-        <v>2015</v>
+        <v>2001</v>
       </c>
       <c r="D117" s="8" t="s">
-        <v>2016</v>
+        <v>2002</v>
       </c>
       <c r="E117" s="8" t="s">
         <v>1639</v>
@@ -14234,16 +14234,16 @@
     </row>
     <row r="118" spans="1:13" ht="84">
       <c r="A118" s="67" t="s">
-        <v>2017</v>
+        <v>2003</v>
       </c>
       <c r="B118" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C118" s="8" t="s">
-        <v>2018</v>
+        <v>2004</v>
       </c>
       <c r="D118" s="8" t="s">
-        <v>2019</v>
+        <v>2005</v>
       </c>
       <c r="E118" s="8" t="s">
         <v>1639</v>
@@ -14264,16 +14264,16 @@
     </row>
     <row r="119" spans="1:13" ht="147">
       <c r="A119" s="67" t="s">
-        <v>2020</v>
+        <v>2006</v>
       </c>
       <c r="B119" s="8" t="s">
         <v>1674</v>
       </c>
       <c r="C119" s="8" t="s">
-        <v>2021</v>
+        <v>2007</v>
       </c>
       <c r="D119" s="8" t="s">
-        <v>2022</v>
+        <v>2008</v>
       </c>
       <c r="E119" s="8" t="s">
         <v>1639</v>
@@ -14300,13 +14300,13 @@
         <v>1667</v>
       </c>
       <c r="C120" s="8" t="s">
-        <v>2023</v>
+        <v>2009</v>
       </c>
       <c r="D120" s="8" t="s">
-        <v>2024</v>
+        <v>2010</v>
       </c>
       <c r="E120" s="8" t="s">
-        <v>2025</v>
+        <v>2011</v>
       </c>
       <c r="F120" s="67"/>
       <c r="G120" s="65">
@@ -14330,10 +14330,10 @@
         <v>1674</v>
       </c>
       <c r="C121" s="8" t="s">
-        <v>2026</v>
+        <v>2012</v>
       </c>
       <c r="D121" s="8" t="s">
-        <v>2027</v>
+        <v>2013</v>
       </c>
       <c r="E121" s="8" t="s">
         <v>1639</v>
@@ -14360,13 +14360,13 @@
         <v>1680</v>
       </c>
       <c r="C122" s="8" t="s">
-        <v>2028</v>
+        <v>2014</v>
       </c>
       <c r="D122" s="8" t="s">
-        <v>2029</v>
+        <v>2015</v>
       </c>
       <c r="E122" s="8" t="s">
-        <v>2025</v>
+        <v>2011</v>
       </c>
       <c r="F122" s="67"/>
       <c r="G122" s="65">
@@ -14416,7 +14416,7 @@
         <v>1644</v>
       </c>
       <c r="D124" s="8" t="s">
-        <v>2030</v>
+        <v>2016</v>
       </c>
       <c r="E124" s="8" t="s">
         <v>1416</v>
@@ -14443,10 +14443,10 @@
         <v>1682</v>
       </c>
       <c r="C125" s="8" t="s">
-        <v>2031</v>
+        <v>2017</v>
       </c>
       <c r="D125" s="8" t="s">
-        <v>2032</v>
+        <v>2018</v>
       </c>
       <c r="E125" s="8" t="s">
         <v>1643</v>
@@ -14473,13 +14473,13 @@
         <v>1667</v>
       </c>
       <c r="C126" s="8" t="s">
-        <v>2033</v>
+        <v>2019</v>
       </c>
       <c r="D126" s="8" t="s">
-        <v>2034</v>
+        <v>2020</v>
       </c>
       <c r="E126" s="8" t="s">
-        <v>2035</v>
+        <v>2021</v>
       </c>
       <c r="F126" s="67"/>
       <c r="G126" s="65">
@@ -14503,10 +14503,10 @@
         <v>1683</v>
       </c>
       <c r="C127" s="8" t="s">
-        <v>2036</v>
+        <v>2022</v>
       </c>
       <c r="D127" s="8" t="s">
-        <v>2037</v>
+        <v>2023</v>
       </c>
       <c r="E127" s="8" t="s">
         <v>2</v>
@@ -14533,13 +14533,13 @@
         <v>36</v>
       </c>
       <c r="C128" s="8" t="s">
-        <v>2038</v>
+        <v>2024</v>
       </c>
       <c r="D128" s="8" t="s">
-        <v>2039</v>
+        <v>2025</v>
       </c>
       <c r="E128" s="8" t="s">
-        <v>1858</v>
+        <v>1852</v>
       </c>
       <c r="F128" s="67"/>
       <c r="G128" s="65">
@@ -14563,10 +14563,10 @@
         <v>1683</v>
       </c>
       <c r="C129" s="8" t="s">
-        <v>2040</v>
+        <v>2026</v>
       </c>
       <c r="D129" s="8" t="s">
-        <v>2041</v>
+        <v>2027</v>
       </c>
       <c r="E129" s="8" t="s">
         <v>1647</v>
@@ -14593,13 +14593,13 @@
         <v>1683</v>
       </c>
       <c r="C130" s="8" t="s">
-        <v>2042</v>
+        <v>2028</v>
       </c>
       <c r="D130" s="8" t="s">
-        <v>2043</v>
+        <v>2029</v>
       </c>
       <c r="E130" s="8" t="s">
-        <v>2044</v>
+        <v>2030</v>
       </c>
       <c r="F130" s="67"/>
       <c r="G130" s="65">
@@ -14623,10 +14623,10 @@
         <v>1680</v>
       </c>
       <c r="C131" s="8" t="s">
-        <v>2045</v>
+        <v>2031</v>
       </c>
       <c r="D131" s="8" t="s">
-        <v>2046</v>
+        <v>2032</v>
       </c>
       <c r="E131" s="8" t="s">
         <v>1642</v>
@@ -14653,10 +14653,10 @@
         <v>1680</v>
       </c>
       <c r="C132" s="8" t="s">
-        <v>2047</v>
+        <v>2033</v>
       </c>
       <c r="D132" s="8" t="s">
-        <v>2048</v>
+        <v>2034</v>
       </c>
       <c r="E132" s="8" t="s">
         <v>1650</v>
@@ -14683,10 +14683,10 @@
         <v>1685</v>
       </c>
       <c r="C133" s="8" t="s">
-        <v>2049</v>
+        <v>2035</v>
       </c>
       <c r="D133" s="8" t="s">
-        <v>2050</v>
+        <v>2036</v>
       </c>
       <c r="E133" s="8" t="s">
         <v>2</v>
@@ -14730,7 +14730,7 @@
     </row>
     <row r="135" spans="1:13" ht="21">
       <c r="A135" s="86" t="s">
-        <v>2051</v>
+        <v>2037</v>
       </c>
       <c r="B135" s="81"/>
       <c r="C135" s="81"/>
@@ -14776,12 +14776,12 @@
   <sheetData>
     <row r="1" spans="1:2" ht="27">
       <c r="A1" s="1" t="s">
-        <v>2052</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="210">
       <c r="A2" s="4" t="s">
-        <v>2053</v>
+        <v>2039</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -14802,7 +14802,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>2054</v>
+        <v>2040</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="126">
@@ -14818,7 +14818,7 @@
         <v>3</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>2055</v>
+        <v>2041</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="168">
@@ -14826,7 +14826,7 @@
         <v>4</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>2056</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="210">
@@ -14842,7 +14842,7 @@
         <v>6</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>2057</v>
+        <v>2043</v>
       </c>
     </row>
     <row r="12" spans="1:2" ht="147">
@@ -14850,17 +14850,17 @@
         <v>7</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>2058</v>
+        <v>2044</v>
       </c>
     </row>
     <row r="14" spans="1:2" ht="252">
       <c r="A14" s="4" t="s">
-        <v>2059</v>
+        <v>2045</v>
       </c>
     </row>
     <row r="15" spans="1:2" ht="231">
       <c r="A15" s="4" t="s">
-        <v>2060</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -14870,7 +14870,7 @@
     </row>
     <row r="18" spans="1:4" ht="409.6">
       <c r="A18" s="4" t="s">
-        <v>2061</v>
+        <v>2047</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -14894,7 +14894,7 @@
     </row>
     <row r="22" spans="1:4">
       <c r="A22" s="63" t="s">
-        <v>2062</v>
+        <v>2048</v>
       </c>
       <c r="B22" s="66">
         <f>SUM('14_WBS'!G2:G7)</f>
@@ -14910,7 +14910,7 @@
     </row>
     <row r="23" spans="1:4">
       <c r="A23" s="63" t="s">
-        <v>2063</v>
+        <v>2049</v>
       </c>
       <c r="B23" s="66">
         <f>SUM('14_WBS'!G9:G33)</f>
@@ -14921,12 +14921,12 @@
         <v>3.625</v>
       </c>
       <c r="D23" s="63" t="s">
-        <v>2064</v>
+        <v>2050</v>
       </c>
     </row>
     <row r="24" spans="1:4">
       <c r="A24" s="63" t="s">
-        <v>2065</v>
+        <v>2051</v>
       </c>
       <c r="B24" s="66">
         <f>SUM('14_WBS'!G35:G44)</f>
@@ -14937,12 +14937,12 @@
         <v>1.625</v>
       </c>
       <c r="D24" s="63" t="s">
-        <v>2066</v>
+        <v>2052</v>
       </c>
     </row>
     <row r="25" spans="1:4">
       <c r="A25" s="63" t="s">
-        <v>2067</v>
+        <v>2053</v>
       </c>
       <c r="B25" s="66">
         <f>SUM('14_WBS'!G46:G79)+SUM('14_WBS'!G81:G93)+SUM('14_WBS'!G95:G112)</f>
@@ -14953,12 +14953,12 @@
         <v>20.1875</v>
       </c>
       <c r="D25" s="63" t="s">
-        <v>2068</v>
+        <v>2054</v>
       </c>
     </row>
     <row r="26" spans="1:4">
       <c r="A26" s="63" t="s">
-        <v>2069</v>
+        <v>2055</v>
       </c>
       <c r="B26" s="66">
         <f>SUM('14_WBS'!G114:G122)</f>
@@ -14969,12 +14969,12 @@
         <v>11.25</v>
       </c>
       <c r="D26" s="63" t="s">
-        <v>2070</v>
+        <v>2056</v>
       </c>
     </row>
     <row r="27" spans="1:4">
       <c r="A27" s="63" t="s">
-        <v>2071</v>
+        <v>2057</v>
       </c>
       <c r="B27" s="66">
         <f>SUM('14_WBS'!G124:G132)</f>
@@ -14985,12 +14985,12 @@
         <v>12.5</v>
       </c>
       <c r="D27" s="63" t="s">
-        <v>2072</v>
+        <v>2058</v>
       </c>
     </row>
     <row r="28" spans="1:4">
       <c r="A28" s="63" t="s">
-        <v>2073</v>
+        <v>2059</v>
       </c>
       <c r="B28" s="66">
         <f>SUM('14_WBS'!G133)</f>
@@ -15006,7 +15006,7 @@
     </row>
     <row r="29" spans="1:4">
       <c r="A29" s="68" t="s">
-        <v>2074</v>
+        <v>2060</v>
       </c>
       <c r="B29" s="69">
         <f>SUM(B22:B28)</f>
@@ -15017,7 +15017,7 @@
         <v>59.6875</v>
       </c>
       <c r="D29" s="68" t="s">
-        <v>2075</v>
+        <v>2061</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -15028,7 +15028,7 @@
     </row>
     <row r="31" spans="1:4" ht="147">
       <c r="A31" s="70" t="s">
-        <v>2076</v>
+        <v>2062</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -15049,10 +15049,10 @@
     </row>
     <row r="35" spans="1:3" ht="21">
       <c r="A35" s="8" t="s">
-        <v>1789</v>
+        <v>1788</v>
       </c>
       <c r="B35" s="8" t="s">
-        <v>2077</v>
+        <v>2063</v>
       </c>
       <c r="C35" s="73">
         <v>2</v>
@@ -15060,10 +15060,10 @@
     </row>
     <row r="36" spans="1:3" ht="21">
       <c r="A36" s="8" t="s">
+        <v>1791</v>
+      </c>
+      <c r="B36" s="8" t="s">
         <v>1792</v>
-      </c>
-      <c r="B36" s="8" t="s">
-        <v>1793</v>
       </c>
       <c r="C36" s="73">
         <v>2</v>
@@ -15071,10 +15071,10 @@
     </row>
     <row r="37" spans="1:3" ht="21">
       <c r="A37" s="8" t="s">
-        <v>2078</v>
+        <v>2064</v>
       </c>
       <c r="B37" s="8" t="s">
-        <v>2079</v>
+        <v>2065</v>
       </c>
       <c r="C37" s="73">
         <v>7</v>
@@ -15082,7 +15082,7 @@
     </row>
     <row r="38" spans="1:3" ht="21">
       <c r="A38" s="8" t="s">
-        <v>1814</v>
+        <v>1813</v>
       </c>
       <c r="B38" s="8" t="s">
         <v>1671</v>
@@ -15096,7 +15096,7 @@
         <v>1640</v>
       </c>
       <c r="B39" s="8" t="s">
-        <v>2023</v>
+        <v>2009</v>
       </c>
       <c r="C39" s="73">
         <v>4</v>
@@ -15107,7 +15107,7 @@
         <v>1646</v>
       </c>
       <c r="B40" s="8" t="s">
-        <v>2033</v>
+        <v>2019</v>
       </c>
       <c r="C40" s="73">
         <v>8</v>
@@ -15125,27 +15125,27 @@
     </row>
     <row r="43" spans="1:3" ht="63">
       <c r="A43" s="9" t="s">
-        <v>2080</v>
+        <v>2066</v>
       </c>
     </row>
     <row r="45" spans="1:3">
       <c r="A45" s="2" t="s">
-        <v>2081</v>
+        <v>2067</v>
       </c>
     </row>
     <row r="46" spans="1:3" ht="126">
       <c r="A46" s="4" t="s">
-        <v>2082</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="47" spans="1:3" ht="84">
       <c r="A47" s="4" t="s">
-        <v>2083</v>
+        <v>2069</v>
       </c>
     </row>
     <row r="48" spans="1:3" ht="63">
       <c r="A48" s="4" t="s">
-        <v>2084</v>
+        <v>2070</v>
       </c>
     </row>
     <row r="50" spans="1:2" ht="21">
@@ -15163,18 +15163,18 @@
     </row>
     <row r="52" spans="1:2" ht="21">
       <c r="A52" s="8" t="s">
-        <v>2085</v>
+        <v>2071</v>
       </c>
       <c r="B52" s="8" t="s">
-        <v>2086</v>
+        <v>2072</v>
       </c>
     </row>
     <row r="53" spans="1:2" ht="21">
       <c r="A53" s="8" t="s">
-        <v>2087</v>
+        <v>2073</v>
       </c>
       <c r="B53" s="8" t="s">
-        <v>2088</v>
+        <v>2074</v>
       </c>
     </row>
     <row r="54" spans="1:2" ht="21">
@@ -15182,43 +15182,43 @@
         <v>1702</v>
       </c>
       <c r="B54" s="8" t="s">
-        <v>2089</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="55" spans="1:2" ht="21">
       <c r="A55" s="8" t="s">
-        <v>2090</v>
+        <v>2076</v>
       </c>
       <c r="B55" s="8" t="s">
-        <v>2091</v>
+        <v>2077</v>
       </c>
     </row>
     <row r="56" spans="1:2" ht="21">
       <c r="A56" s="8" t="s">
-        <v>2092</v>
+        <v>2078</v>
       </c>
       <c r="B56" s="8" t="s">
-        <v>2093</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="58" spans="1:2" ht="21">
       <c r="A58" s="10" t="s">
-        <v>2094</v>
+        <v>2080</v>
       </c>
     </row>
     <row r="59" spans="1:2" ht="63">
       <c r="A59" s="4" t="s">
-        <v>2095</v>
+        <v>2081</v>
       </c>
     </row>
     <row r="60" spans="1:2" ht="63">
       <c r="A60" s="4" t="s">
-        <v>2096</v>
+        <v>2082</v>
       </c>
     </row>
     <row r="61" spans="1:2" ht="42">
       <c r="A61" s="4" t="s">
-        <v>2097</v>
+        <v>2083</v>
       </c>
     </row>
   </sheetData>

--- a/doc/excel/apipf.xlsx
+++ b/doc/excel/apipf.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suepie/Develop/10_project/aws-atuh-poc/doc/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3DF9A48A-C753-B740-90B5-61BBA5D21DA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582C47CA-38F5-B946-948D-50D475574B80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" firstSheet="5" activeTab="13" xr2:uid="{3DFCE3C5-E09C-1942-8E2D-30A61B5A45AE}"/>
+    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" firstSheet="7" activeTab="13" xr2:uid="{3DFCE3C5-E09C-1942-8E2D-30A61B5A45AE}"/>
   </bookViews>
   <sheets>
     <sheet name="01_表紙・改訂履歴" sheetId="1" r:id="rId1"/>

--- a/doc/excel/apipf.xlsx
+++ b/doc/excel/apipf.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/suepie/Develop/10_project/aws-atuh-poc/doc/excel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{971EC070-5EDD-B043-B888-D372AA9A9290}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C5184F-EE4F-6C41-B576-07F979F2E8B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21460" firstSheet="7" activeTab="13" xr2:uid="{3DFCE3C5-E09C-1942-8E2D-30A61B5A45AE}"/>
   </bookViews>
